--- a/過去売上高/売上高202608.xlsx
+++ b/過去売上高/売上高202608.xlsx
@@ -610,7 +610,7 @@
       <c r="E1" s="5" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>choccoメロンパン</t>
+          <t>メロンパン</t>
         </is>
       </c>
       <c r="G1" s="4" t="n"/>
